--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.91154049550831</v>
+        <v>9.248125330520102</v>
       </c>
       <c r="D2" t="n">
-        <v>56.70842381028055</v>
+        <v>9.21511886917059</v>
       </c>
       <c r="E2" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F2" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.2769856019231</v>
+        <v>9.145010160312504</v>
       </c>
       <c r="D3" t="n">
-        <v>56.34922027640143</v>
+        <v>9.156748294915234</v>
       </c>
       <c r="E3" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F3" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.89830592488541</v>
+        <v>4.858474712793879</v>
       </c>
       <c r="D4" t="n">
-        <v>29.60087030774487</v>
+        <v>4.810141425008541</v>
       </c>
       <c r="E4" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F4" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.89760654826495</v>
+        <v>7.458361064093054</v>
       </c>
       <c r="D5" t="n">
-        <v>45.89565020838545</v>
+        <v>7.458043158862635</v>
       </c>
       <c r="E5" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F5" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.62731520511083</v>
+        <v>4.97693872083051</v>
       </c>
       <c r="D6" t="n">
-        <v>30.6038789209586</v>
+        <v>4.973130324655773</v>
       </c>
       <c r="E6" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F6" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9820038612442</v>
+        <v>3.409575627452182</v>
       </c>
       <c r="D7" t="n">
-        <v>20.98033656217791</v>
+        <v>3.409304691353911</v>
       </c>
       <c r="E7" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F7" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.42442162456468</v>
+        <v>6.731468513991761</v>
       </c>
       <c r="D8" t="n">
-        <v>41.38546614468184</v>
+        <v>6.725138248510799</v>
       </c>
       <c r="E8" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F8" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>69.12641495476167</v>
+        <v>11.23304243014877</v>
       </c>
       <c r="D9" t="n">
-        <v>69.05743091992153</v>
+        <v>11.22183252448725</v>
       </c>
       <c r="E9" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F9" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.76186067470036</v>
+        <v>8.086302359638809</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68633945712573</v>
+        <v>8.074030161782931</v>
       </c>
       <c r="E10" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F10" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>73.5140572538387</v>
+        <v>11.94603430374879</v>
       </c>
       <c r="D11" t="n">
-        <v>73.44158026940862</v>
+        <v>11.9342567937789</v>
       </c>
       <c r="E11" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F11" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.50497627075191</v>
+        <v>9.182058643997186</v>
       </c>
       <c r="D12" t="n">
-        <v>56.44092050314821</v>
+        <v>9.171649581761583</v>
       </c>
       <c r="E12" t="n">
-        <v>15.74509797167917</v>
+        <v>2.558578420397866</v>
       </c>
       <c r="F12" t="n">
-        <v>15.75177824037193</v>
+        <v>2.559663964060439</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
